--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.51.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.51.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.51.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.51.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.51.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.51.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0051.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0051.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -598,11 +598,15 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 'â€¢ scr</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]44</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]44</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L16: isolated marker/symbol line :: 44</t>
@@ -610,7 +614,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L68: isolated marker/symbol line :: T</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]44</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -645,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -657,7 +661,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L123: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ /</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: '• scr</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -669,7 +673,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: Â«</t>
+          <t>L39: isolated marker/symbol line :: «1</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -706,7 +710,11 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>L123: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • /</t>
+        </is>
+      </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -716,7 +724,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L121: isolated marker/symbol line :: # -</t>
+          <t>L51: isolated marker/symbol line :: «r</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -743,7 +751,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -761,7 +769,11 @@
           <t>L50: symbol-only separator/garbage line :: 113.</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L52: symbol-only separator/garbage line :: «____</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -800,7 +812,11 @@
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr"/>
-      <c r="O6" s="1" t="inlineStr"/>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>L68: isolated marker/symbol line :: T</t>
+        </is>
+      </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr"/>
@@ -839,7 +855,11 @@
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr"/>
-      <c r="O7" s="1" t="inlineStr"/>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>L70: isolated marker/symbol line :: «</t>
+        </is>
+      </c>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr"/>
       <c r="R7" s="1" t="inlineStr"/>
@@ -878,7 +898,11 @@
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr"/>
-      <c r="O8" s="1" t="inlineStr"/>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>L121: isolated marker/symbol line :: # -</t>
+        </is>
+      </c>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr"/>
@@ -917,7 +941,11 @@
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr"/>
-      <c r="O9" s="1" t="inlineStr"/>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>L123: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • /</t>
+        </is>
+      </c>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
       <c r="R9" s="1" t="inlineStr"/>
@@ -942,7 +970,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -981,7 +1009,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1020,7 +1048,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
